--- a/data/trans_camb/P6904-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 30,98</t>
+          <t>-38,4; 33,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 29,02</t>
+          <t>-27,12; 29,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 58,26</t>
+          <t>-52,79; 58,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 14,52</t>
+          <t>-56,16; 13,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 35,83</t>
+          <t>-32,32; 36,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 22,54</t>
+          <t>-56,31; 21,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 14,34</t>
+          <t>-34,87; 12,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 23,08</t>
+          <t>-16,29; 24,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 16,28</t>
+          <t>-40,79; 17,87</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,77; 79,37</t>
+          <t>-75,51; 81,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 77,37</t>
+          <t>-49,18; 77,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,91</t>
+          <t>-100,0; 145,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-84,33; 29,53</t>
+          <t>-82,2; 30,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,54; 74,0</t>
+          <t>-44,7; 75,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,94; 46,58</t>
+          <t>-83,46; 41,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,97; 32,86</t>
+          <t>-60,77; 28,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 51,06</t>
+          <t>-28,99; 56,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 33,26</t>
+          <t>-75,23; 38,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 19,78</t>
+          <t>-6,69; 20,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 24,14</t>
+          <t>-3,58; 24,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 31,42</t>
+          <t>-5,58; 31,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 21,85</t>
+          <t>-13,36; 21,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 38,29</t>
+          <t>1,81; 36,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 26,88</t>
+          <t>-8,82; 27,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 17,14</t>
+          <t>-5,88; 16,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 25,07</t>
+          <t>3,75; 25,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 24,81</t>
+          <t>-1,04; 24,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 47,74</t>
+          <t>-11,84; 48,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 57,5</t>
+          <t>-6,07; 58,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 75,02</t>
+          <t>-10,67; 73,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 61,0</t>
+          <t>-25,81; 63,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 113,61</t>
+          <t>3,48; 104,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 73,98</t>
+          <t>-18,7; 77,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 41,54</t>
+          <t>-11,35; 40,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 60,35</t>
+          <t>6,55; 60,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 60,2</t>
+          <t>-1,21; 58,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 12,04</t>
+          <t>-14,04; 13,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 18,67</t>
+          <t>-5,87; 20,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 16,44</t>
+          <t>-11,8; 16,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 15,39</t>
+          <t>-17,16; 15,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 23,65</t>
+          <t>-8,03; 24,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 16,46</t>
+          <t>-15,69; 16,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 9,41</t>
+          <t>-11,64; 9,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 17,18</t>
+          <t>-3,57; 16,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 11,15</t>
+          <t>-8,68; 11,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 22,62</t>
+          <t>-22,31; 25,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 35,98</t>
+          <t>-8,86; 39,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 33,14</t>
+          <t>-18,21; 30,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 31,69</t>
+          <t>-26,18; 30,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 49,63</t>
+          <t>-12,72; 54,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 35,7</t>
+          <t>-23,26; 36,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 17,16</t>
+          <t>-18,92; 17,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 32,69</t>
+          <t>-5,52; 32,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 21,02</t>
+          <t>-13,9; 22,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 17,8</t>
+          <t>-13,28; 17,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 22,56</t>
+          <t>-9,23; 21,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 28,91</t>
+          <t>2,14; 30,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 4,51</t>
+          <t>-41,18; 2,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 19,92</t>
+          <t>-19,36; 19,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 32,98</t>
+          <t>-5,74; 33,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 9,71</t>
+          <t>-15,96; 9,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 18,63</t>
+          <t>-5,16; 17,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 30,53</t>
+          <t>6,81; 31,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 46,04</t>
+          <t>-24,91; 41,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 57,94</t>
+          <t>-16,9; 53,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 76,0</t>
+          <t>3,9; 77,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 7,17</t>
+          <t>-55,37; 3,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 41,48</t>
+          <t>-27,24; 39,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 65,24</t>
+          <t>-8,57; 71,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 20,67</t>
+          <t>-28,41; 21,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 40,21</t>
+          <t>-8,99; 38,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,02; 66,59</t>
+          <t>11,34; 68,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 14,35</t>
+          <t>-26,6; 15,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 22,03</t>
+          <t>-19,41; 21,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 18,43</t>
+          <t>-17,25; 19,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 66,23</t>
+          <t>3,26; 64,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,68; 81,31</t>
+          <t>21,84; 79,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,7; 64,09</t>
+          <t>14,5; 64,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 25,79</t>
+          <t>-8,47; 25,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 33,57</t>
+          <t>1,28; 35,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 23,4</t>
+          <t>-3,32; 27,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 26,37</t>
+          <t>-38,27; 29,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 44,26</t>
+          <t>-28,15; 41,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 36,93</t>
+          <t>-24,77; 40,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,73; 869,8</t>
+          <t>4,35; 594,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52,4; 1179,08</t>
+          <t>38,03; 606,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,0; 894,89</t>
+          <t>29,59; 956,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 60,17</t>
+          <t>-13,86; 61,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 75,18</t>
+          <t>2,15; 82,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 52,7</t>
+          <t>-4,87; 62,45</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 10,3</t>
+          <t>-4,68; 10,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 13,99</t>
+          <t>0,07; 14,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,56; 16,46</t>
+          <t>1,59; 16,34</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 9,21</t>
+          <t>-10,06; 8,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,56; 24,63</t>
+          <t>6,34; 24,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,84; 25,38</t>
+          <t>4,7; 25,75</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 7,42</t>
+          <t>-4,55; 7,75</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4,49; 16,13</t>
+          <t>4,89; 16,14</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,64; 17,91</t>
+          <t>5,54; 17,43</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 20,97</t>
+          <t>-8,45; 21,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 27,9</t>
+          <t>0,2; 29,9</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,88; 33,9</t>
+          <t>2,79; 33,37</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 19,86</t>
+          <t>-17,56; 18,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,58; 54,02</t>
+          <t>10,71; 51,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,3; 54,0</t>
+          <t>7,51; 52,87</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 15,19</t>
+          <t>-8,52; 16,0</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,28; 32,51</t>
+          <t>9,09; 32,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10,6; 36,72</t>
+          <t>10,16; 35,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6904-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-17,63</t>
+          <t>7,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-22,18</t>
+          <t>-21,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,6</t>
+          <t>-5,53</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 33,56</t>
+          <t>-34,38; 33,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 29,19</t>
+          <t>-28,9; 28,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 58,15</t>
+          <t>-49,78; 51,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 13,66</t>
+          <t>-58,15; 16,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 36,54</t>
+          <t>-30,07; 35,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 21,51</t>
+          <t>-54,42; 23,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 12,88</t>
+          <t>-36,02; 12,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 24,91</t>
+          <t>-18,67; 26,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 17,87</t>
+          <t>-35,1; 23,28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-36,91%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,3%</t>
+          <t>-33,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-27,91%</t>
+          <t>-10,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 81,88</t>
+          <t>-71,18; 80,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 77,44</t>
+          <t>-53,51; 71,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,63</t>
+          <t>-100,0; 126,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,2; 30,2</t>
+          <t>-84,46; 35,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 75,25</t>
+          <t>-38,77; 75,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,46; 41,71</t>
+          <t>-76,97; 52,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 28,1</t>
+          <t>-64,96; 28,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 56,69</t>
+          <t>-31,1; 60,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,23; 38,19</t>
+          <t>-61,24; 49,41</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>15,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,61</t>
+          <t>13,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 20,42</t>
+          <t>-6,01; 21,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 24,84</t>
+          <t>-3,23; 23,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 31,7</t>
+          <t>-2,55; 32,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 21,26</t>
+          <t>-13,15; 22,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 36,02</t>
+          <t>2,34; 37,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 27,36</t>
+          <t>-7,94; 27,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 16,85</t>
+          <t>-3,12; 17,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 25,0</t>
+          <t>3,05; 26,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 24,18</t>
+          <t>1,06; 26,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 48,03</t>
+          <t>-11,3; 53,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 58,53</t>
+          <t>-6,39; 55,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 73,7</t>
+          <t>-4,93; 76,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 63,18</t>
+          <t>-27,18; 65,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 104,54</t>
+          <t>4,83; 108,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 77,33</t>
+          <t>-16,74; 76,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 40,75</t>
+          <t>-6,4; 41,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 60,28</t>
+          <t>7,02; 64,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 58,63</t>
+          <t>2,05; 63,8</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 13,22</t>
+          <t>-14,08; 13,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 20,31</t>
+          <t>-8,55; 17,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 16,48</t>
+          <t>-10,15; 17,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 15,85</t>
+          <t>-18,71; 15,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 24,52</t>
+          <t>-10,63; 23,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 16,55</t>
+          <t>-15,66; 12,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 9,23</t>
+          <t>-12,25; 9,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 16,5</t>
+          <t>-3,66; 15,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 11,83</t>
+          <t>-9,07; 11,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0,03%</t>
+          <t>-3,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 25,23</t>
+          <t>-22,17; 26,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 39,94</t>
+          <t>-12,95; 33,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 30,7</t>
+          <t>-15,91; 31,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 30,54</t>
+          <t>-28,68; 29,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 54,82</t>
+          <t>-15,91; 47,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 36,57</t>
+          <t>-23,61; 27,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 17,29</t>
+          <t>-19,09; 17,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 32,13</t>
+          <t>-5,6; 29,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 22,52</t>
+          <t>-14,33; 23,01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>17,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,71</t>
+          <t>13,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 17,03</t>
+          <t>-11,52; 17,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 21,46</t>
+          <t>-6,37; 21,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 30,54</t>
+          <t>1,82; 28,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 2,32</t>
+          <t>-41,78; 5,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 19,89</t>
+          <t>-19,66; 20,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 33,93</t>
+          <t>-15,91; 20,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 9,84</t>
+          <t>-14,93; 9,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 17,93</t>
+          <t>-4,97; 18,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 31,43</t>
+          <t>4,07; 25,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 41,44</t>
+          <t>-20,98; 42,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 53,96</t>
+          <t>-12,21; 53,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,9; 77,05</t>
+          <t>4,17; 71,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 3,66</t>
+          <t>-56,48; 8,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 39,74</t>
+          <t>-27,26; 36,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 71,0</t>
+          <t>-20,56; 40,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 21,87</t>
+          <t>-26,98; 20,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 38,64</t>
+          <t>-8,32; 41,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,34; 68,83</t>
+          <t>6,97; 57,31</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,77</t>
+          <t>40,76</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 15,18</t>
+          <t>-24,78; 17,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 21,08</t>
+          <t>-18,51; 22,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 19,54</t>
+          <t>-17,46; 20,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,26; 64,57</t>
+          <t>5,43; 65,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,84; 79,11</t>
+          <t>27,09; 82,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,5; 64,24</t>
+          <t>9,34; 62,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 25,67</t>
+          <t>-10,36; 26,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 35,29</t>
+          <t>1,66; 34,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 27,09</t>
+          <t>-2,38; 27,9</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>151,5%</t>
+          <t>147,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 29,81</t>
+          <t>-34,03; 33,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 41,05</t>
+          <t>-26,85; 43,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 40,05</t>
+          <t>-23,96; 40,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4,35; 594,04</t>
+          <t>8,44; 881,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>38,03; 606,57</t>
+          <t>50,1; 1179,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,59; 956,0</t>
+          <t>16,12; 910,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 61,27</t>
+          <t>-16,83; 58,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,15; 82,32</t>
+          <t>3,48; 82,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 62,45</t>
+          <t>-3,49; 66,32</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>9,2</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,35</t>
+          <t>10,08</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 10,44</t>
+          <t>-4,44; 10,88</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,07; 14,69</t>
+          <t>0,59; 15,06</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,34</t>
+          <t>3,99; 18,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 8,83</t>
+          <t>-9,82; 9,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,34; 24,1</t>
+          <t>5,95; 24,23</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,7; 25,75</t>
+          <t>0,39; 17,01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 7,75</t>
+          <t>-4,35; 7,32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4,89; 16,14</t>
+          <t>4,77; 16,24</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,54; 17,43</t>
+          <t>4,77; 15,4</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 21,19</t>
+          <t>-8,12; 21,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,2; 29,9</t>
+          <t>1,06; 30,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,79; 33,37</t>
+          <t>7,19; 37,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 18,63</t>
+          <t>-17,65; 19,28</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,71; 51,4</t>
+          <t>10,39; 52,6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,51; 52,87</t>
+          <t>0,69; 36,95</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 16,0</t>
+          <t>-7,96; 14,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,09; 32,63</t>
+          <t>9,31; 32,96</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10,16; 35,26</t>
+          <t>8,84; 31,3</t>
         </is>
       </c>
     </row>
